--- a/plan/robot_project_plan_v2.xlsx
+++ b/plan/robot_project_plan_v2.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Stage 3 = build the duck's legs and put the OreVis shell, face and camera on top. Keep added mass under about 150 g. See sim/OPEN_DUCK.md</t>
+          <t>Stage 3 = build the duck's legs and put the round robot shell, face and camera on top. Keep added mass under about 150 g. See sim/OPEN_DUCK.md</t>
         </is>
       </c>
     </row>
@@ -883,59 +883,103 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Software: write behaviours once, run them in the twin and on the robot</t>
+          <t>Use Pollen Robotics' open-source Amazing Hand files</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Give motors, servos and sensors the same small interface in the sandbox, MuJoCo and the robot. Tested behaviour code can then move to hardware unchanged.</t>
+          <t>Pollen publish the hand's print files (CC BY 4.0), servo code and a MuJoCo model (Apache 2.0). A copy is in third_party/pollen; python sim/amazing_hand.py runs their model through their named poses. Closed, the fingertips stop about 46 mm from the thumb, so tip-to-tip it can't pinch the 30 mm test blocks.</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>New software row 10: hal.py</t>
+          <t>Use their files as-is for the bench-mounted hand; test with 50 mm objects first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Adapt</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>P04 does not need to wait for parts (P03)</t>
+          <t>Stage 5 voice: start from Pollen's Reachy Mini conversation app</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>The computer, Thonny and the sandbox can all be set up while parts ship.</t>
+          <t>Reachy Mini's SDK and conversation app are open source (Apache 2.0) and already connect a microphone, a speaker and a language model to a small robot.</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>P04 dependency changed to None</t>
+          <t>third_party/fetch_pollen.sh downloads it; adapt its voice loop for P30-P31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
+          <t>Adapt</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Software: write behaviours once, run them in the twin and on the robot</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Give motors, servos and sensors the same small interface in the sandbox, MuJoCo and the robot. Tested behaviour code can then move to hardware unchanged.</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>New software row 10: hal.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
           <t>Fix</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>P04 does not need to wait for parts (P03)</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>The computer, Thonny and the sandbox can all be set up while parts ship.</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>P04 dependency changed to None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>P18 live video now has a home</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Stage 2 adds the Pi Zero 2 W, which streams the camera. The Pico keeps doing motors and the face.</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>P18 linked to stage 2 tasks</t>
         </is>
@@ -1891,7 +1935,7 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Stage 3: OreVis head on the duck</t>
+          <t>Stage 3: robot head on the duck</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -2321,7 +2365,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Grows legs: Open Duck Mini v2 legs (10x STS3215), BNO055 IMU, 2S battery. OreVis shell becomes the head and body.</t>
+          <t>Grows legs: Open Duck Mini v2 legs (10x STS3215), BNO055 IMU, 2S battery. The round robot shell becomes the head and body.</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -3930,12 +3974,12 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Pollen Amazing Hand kit (optional)</t>
+          <t>Pollen Amazing Hand (optional): 8x Feetech SCS0009 + printed parts</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>8 servos, about 400 g. Too heavy for the walker; use on a bench arm.</t>
+          <t>Free print files and code from Pollen (third_party/pollen). About 400 g: too heavy for the walker, use on a bench arm.</t>
         </is>
       </c>
       <c r="D38" s="23" t="n">
@@ -3950,7 +3994,7 @@
       </c>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>https://huggingface.co/blog/pollen-robotics/amazing-hand</t>
+          <t>https://github.com/pollen-robotics/AmazingHand</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">
@@ -4564,7 +4608,7 @@
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Wake word, then speech-to-text, then the same command parser as the sandbox. Say 'stop' always wins.</t>
+          <t>Start from Pollen's Reachy Mini conversation app (third_party/fetch_pollen.sh). Speech goes to the same command parser as the sandbox. 'Stop' always wins.</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -4574,7 +4618,7 @@
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>https://github.com/rhasspy/piper</t>
+          <t>https://github.com/pollen-robotics/reachy_mini</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">

--- a/plan/robot_project_plan_v2.xlsx
+++ b/plan/robot_project_plan_v2.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Pollen's Amazing Hand is about 400 g. The physics bench shows the 1.36 kg walker tips 44 degrees holding it out. A 45 g 3-finger tendon hand holds a 20 g block at 64% of shoulder stall with no tipping.</t>
+          <t>Pollen's Amazing Hand is about 400 g. The physics bench shows the 1.36 kg walker tips 37 degrees holding it out. A 45 g 3-finger tendon hand holds a 20 g block at 64% of shoulder stall with no tipping.</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="J11" s="17" t="n">
-        <v>43.6</v>
+        <v>36.5</v>
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>

--- a/plan/robot_project_plan_v2.xlsx
+++ b/plan/robot_project_plan_v2.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -817,17 +817,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Use one servo family for legs, arm and hand</t>
+          <t>Walking runs on the Open Duck's own trained policy</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Feetech serial-bus servos (STS3215, SCS0009) share one 3-wire bus and one driver board, and report their angle. Open Duck, the LeRobot SO-101 arm and Pollen's Amazing Hand all use them.</t>
+          <t>sim/open_duck_walk.py runs the Open Duck Mini's published policy in MuJoCo. It walked forward (0.096 m/s), turned (about 47 deg/s) and walked backwards for 21 s without falling. The sandbox plays that recorded gait on the robot's legs. The duck's hips attach about 21 cm up, so the robot shell replaces the duck's body with the hip motors inside it.</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>Standardise on Feetech bus servos for stages 3 to 5</t>
+          <t>Stage 3: shell replaces the duck's body; run python sim/open_duck_walk.py before building</t>
         </is>
       </c>
     </row>
@@ -839,17 +839,17 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Hand: start with a light 3-finger hand, not the full humanoid hand</t>
+          <t>Use one servo family for legs, arm and hand</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Pollen's Amazing Hand is about 400 g. The physics bench shows the 1.36 kg walker tips 37 degrees holding it out. A 45 g 3-finger tendon hand holds a 20 g block at 64% of shoulder stall with no tipping.</t>
+          <t>Feetech serial-bus servos (STS3215, SCS0009) share one 3-wire bus and one driver board, and report their angle. Open Duck, the LeRobot SO-101 arm and Pollen's Amazing Hand all use them.</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Stage 4 = 3-finger hand. Try the Amazing Hand later on a bench-mounted arm</t>
+          <t>Standardise on Feetech bus servos for stages 3 to 5</t>
         </is>
       </c>
     </row>
@@ -861,17 +861,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>A walking robot must squat to pick things off the floor</t>
+          <t>Hand: start with a light 3-finger hand, not the full humanoid hand</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Sandbox: with a 17 cm arm mounted 26 cm up, the Helper only reaches the floor by squatting about 63 degrees at the knee. The bench shows STS3215 knees peak at 36% of stall in that squat, which is fine.</t>
+          <t>Pollen's Amazing Hand is about 400 g. The physics bench shows the 1.36 kg walker tips 37 degrees holding it out. A 45 g 3-finger tendon hand holds a 20 g block at 64% of shoulder stall with no tipping.</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Add a squat-and-reach behaviour (sandbox already does it)</t>
+          <t>Stage 4 = 3-finger hand. Try the Amazing Hand later on a bench-mounted arm</t>
         </is>
       </c>
     </row>
@@ -883,17 +883,17 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Use Pollen Robotics' open-source Amazing Hand files</t>
+          <t>A walking robot must squat to pick things off the floor</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Pollen publish the hand's print files (CC BY 4.0), servo code and a MuJoCo model (Apache 2.0). A copy is in third_party/pollen; python sim/amazing_hand.py runs their model through their named poses. Closed, the fingertips stop about 46 mm from the thumb, so tip-to-tip it can't pinch the 30 mm test blocks.</t>
+          <t>Sandbox: with a 17 cm arm mounted 26 cm up, the Helper only reaches the floor by squatting about 63 degrees at the knee. The bench shows STS3215 knees peak at 36% of stall in that squat, which is fine.</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Use their files as-is for the bench-mounted hand; test with 50 mm objects first</t>
+          <t>Add a squat-and-reach behaviour (sandbox already does it)</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Stage 5 voice: start from Pollen's Reachy Mini conversation app</t>
+          <t>Use Pollen Robotics' open-source Amazing Hand files</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Reachy Mini's SDK and conversation app are open source (Apache 2.0) and already connect a microphone, a speaker and a language model to a small robot.</t>
+          <t>Pollen publish the hand's print files (CC BY 4.0), servo code and a MuJoCo model (Apache 2.0). A copy is in third_party/pollen; python sim/amazing_hand.py runs their model through their named poses. Closed, the fingertips stop about 46 mm from the thumb, so tip-to-tip it can't pinch the 30 mm test blocks.</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>third_party/fetch_pollen.sh downloads it; adapt its voice loop for P30-P31</t>
+          <t>Use their files as-is for the bench-mounted hand; test with 50 mm objects first</t>
         </is>
       </c>
     </row>
@@ -927,39 +927,39 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Software: write behaviours once, run them in the twin and on the robot</t>
+          <t>Stage 5 voice: start from Pollen's Reachy Mini conversation app</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Give motors, servos and sensors the same small interface in the sandbox, MuJoCo and the robot. Tested behaviour code can then move to hardware unchanged.</t>
+          <t>Reachy Mini's SDK and conversation app are open source (Apache 2.0) and already connect a microphone, a speaker and a language model to a small robot.</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>New software row 10: hal.py</t>
+          <t>third_party/fetch_pollen.sh downloads it; adapt its voice loop for P30-P31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Fix</t>
+          <t>Adapt</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>P04 does not need to wait for parts (P03)</t>
+          <t>Software: write behaviours once, run them in the twin and on the robot</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>The computer, Thonny and the sandbox can all be set up while parts ship.</t>
+          <t>Give motors, servos and sensors the same small interface in the sandbox, MuJoCo and the robot. Tested behaviour code can then move to hardware unchanged.</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>P04 dependency changed to None</t>
+          <t>New software row 10: hal.py</t>
         </is>
       </c>
     </row>
@@ -971,15 +971,37 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
+          <t>P04 does not need to wait for parts (P03)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>The computer, Thonny and the sandbox can all be set up while parts ship.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>P04 dependency changed to None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
           <t>P18 live video now has a home</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Stage 2 adds the Pi Zero 2 W, which streams the camera. The Pico keeps doing motors and the face.</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>P18 linked to stage 2 tasks</t>
         </is>
@@ -1812,7 +1834,7 @@
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>Install uv and Open_Duck_Playground. Run mujoco_infer.py with a trained policy and watch the duck walk. No hardware needed.</t>
+          <t>Run third_party/fetch_open_duck.sh, then python sim/open_duck_walk.py --view and watch the trained policy walk the duck. No hardware needed.</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -1822,7 +1844,7 @@
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>2-3 hours</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
